--- a/begunici/app_types/animals/excel_templates/archive_acts/zaboi.xlsx
+++ b/begunici/app_types/animals/excel_templates/archive_acts/zaboi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\archive_acts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A8488-3C70-4153-A6CB-66586AE12252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199ACA1E-A9D3-43DA-93EC-6639DD7A3195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>по ОКПО</t>
-  </si>
-  <si>
-    <t>ООО "Бегуницы"</t>
   </si>
   <si>
     <t>Организация</t>
@@ -189,6 +186,9 @@
     <t>Воз-
 раст,
 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ООО "Ферма "Бегуницы"												</t>
   </si>
 </sst>
 </file>
@@ -657,7 +657,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -721,90 +721,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -822,26 +746,91 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1124,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E860CC0-4791-4AE8-9553-026103C94BE3}">
-  <dimension ref="A1:AQ27"/>
+  <dimension ref="A1:AP27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="2" customWidth="1"/>
@@ -1170,400 +1159,400 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI1" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI2" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI3" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="X4" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="X4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
     </row>
     <row r="5" spans="1:42" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="U5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN5" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="AO5" s="32"/>
-      <c r="AP5" s="33"/>
+      <c r="AN5" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO5" s="42"/>
+      <c r="AP5" s="43"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="U6" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="34"/>
-      <c r="W6" s="34"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="34"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="34"/>
-      <c r="AC6" s="34"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="34"/>
-      <c r="AJ6" s="35" t="s">
+      <c r="U6" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AK6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AN6" s="36" t="s">
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="44"/>
+      <c r="Z6" s="44"/>
+      <c r="AA6" s="44"/>
+      <c r="AB6" s="44"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="44"/>
+      <c r="AE6" s="44"/>
+      <c r="AJ6" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="AO6" s="37"/>
-      <c r="AP6" s="38"/>
+      <c r="AK6" s="34"/>
+      <c r="AL6" s="34"/>
+      <c r="AN6" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="47"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="AJ7" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK7" s="35"/>
-      <c r="AL7" s="35"/>
+      <c r="AJ7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="34"/>
       <c r="AN7" s="22"/>
       <c r="AO7" s="21"/>
       <c r="AP7" s="20"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="35" t="s">
+      <c r="F8" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="AL8" s="35"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="28"/>
+      <c r="AL8" s="34"/>
+      <c r="AN8" s="35"/>
+      <c r="AO8" s="36"/>
+      <c r="AP8" s="37"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
-      <c r="S9" s="56"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="56"/>
-      <c r="Y9" s="56"/>
-      <c r="Z9" s="56"/>
-      <c r="AA9" s="56"/>
-      <c r="AB9" s="56"/>
-      <c r="AC9" s="56"/>
-      <c r="AD9" s="56"/>
-      <c r="AE9" s="56"/>
-      <c r="AF9" s="56"/>
-      <c r="AG9" s="56"/>
-      <c r="AH9" s="56"/>
-      <c r="AI9" s="56"/>
-      <c r="AJ9" s="56"/>
-      <c r="AK9" s="56"/>
-      <c r="AL9" s="56"/>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="28"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="37"/>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="56"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="56"/>
-      <c r="AH10" s="56"/>
-      <c r="AI10" s="56"/>
-      <c r="AJ10" s="56"/>
-      <c r="AK10" s="56"/>
-      <c r="AL10" s="56"/>
-      <c r="AN10" s="26"/>
-      <c r="AO10" s="27"/>
-      <c r="AP10" s="28"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AN10" s="35"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="37"/>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
-      <c r="AJ11" s="25"/>
-      <c r="AK11" s="25"/>
-      <c r="AL11" s="25"/>
-      <c r="AN11" s="26"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="28"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="38"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="38"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="37"/>
     </row>
     <row r="12" spans="1:42" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="56"/>
-      <c r="Z12" s="56"/>
-      <c r="AA12" s="56"/>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="56"/>
-      <c r="AD12" s="56"/>
-      <c r="AE12" s="56"/>
-      <c r="AF12" s="56"/>
-      <c r="AG12" s="56"/>
-      <c r="AH12" s="56"/>
-      <c r="AI12" s="56"/>
-      <c r="AJ12" s="56"/>
-      <c r="AK12" s="56"/>
-      <c r="AL12" s="56"/>
-      <c r="AN12" s="57"/>
-      <c r="AO12" s="58"/>
-      <c r="AP12" s="59"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="32"/>
+      <c r="AP12" s="33"/>
     </row>
     <row r="13" spans="1:42" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="14" spans="1:42" ht="49.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="51" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="53"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="62"/>
       <c r="M14" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="54" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="51" t="s">
+      <c r="N14" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="R14" s="52"/>
-      <c r="S14" s="53"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="62"/>
       <c r="T14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="U14" s="55" t="s">
+      <c r="U14" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="55" t="s">
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Y14" s="55"/>
-      <c r="Z14" s="55"/>
-      <c r="AA14" s="60" t="s">
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="60"/>
-      <c r="AD14" s="60"/>
-      <c r="AE14" s="61" t="s">
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62" t="s">
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="27"/>
+      <c r="AH14" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="54" t="s">
+      <c r="AI14" s="27"/>
+      <c r="AJ14" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AK14" s="54"/>
-      <c r="AL14" s="54"/>
-      <c r="AM14" s="54"/>
-      <c r="AN14" s="62" t="s">
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="28"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
+      <c r="AO14" s="27"/>
+      <c r="AP14" s="27"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="49"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="58"/>
       <c r="M15" s="16"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="59"/>
+      <c r="R15" s="59"/>
+      <c r="S15" s="59"/>
       <c r="T15" s="17"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="42"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="44"/>
-      <c r="AO15" s="44"/>
-      <c r="AP15" s="44"/>
-    </row>
-    <row r="17" spans="1:43" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="48"/>
+      <c r="X15" s="48"/>
+      <c r="Y15" s="48"/>
+      <c r="Z15" s="48"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="48"/>
+      <c r="AC15" s="48"/>
+      <c r="AD15" s="50"/>
+      <c r="AE15" s="51"/>
+      <c r="AF15" s="52"/>
+      <c r="AG15" s="52"/>
+      <c r="AH15" s="52"/>
+      <c r="AI15" s="52"/>
+      <c r="AJ15" s="52"/>
+      <c r="AK15" s="52"/>
+      <c r="AL15" s="52"/>
+      <c r="AM15" s="52"/>
+      <c r="AN15" s="53"/>
+      <c r="AO15" s="53"/>
+      <c r="AP15" s="53"/>
+    </row>
+    <row r="17" spans="1:42" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -1595,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.45">
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
@@ -1610,7 +1599,7 @@
       <c r="AG18" s="4"/>
       <c r="AH18" s="14"/>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.45">
       <c r="U19" s="2" t="s">
         <v>8</v>
       </c>
@@ -1639,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>6</v>
       </c>
@@ -1672,17 +1661,16 @@
       <c r="AD21" s="10"/>
       <c r="AE21" s="10"/>
       <c r="AH21" s="12"/>
-      <c r="AI21" s="65"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="64"/>
-      <c r="AL21" s="64"/>
-      <c r="AM21" s="64"/>
-      <c r="AN21" s="64"/>
-      <c r="AO21" s="64"/>
-      <c r="AP21" s="64"/>
-      <c r="AQ21" s="67"/>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="11"/>
+      <c r="AK21" s="11"/>
+      <c r="AL21" s="11"/>
+      <c r="AM21" s="11"/>
+      <c r="AN21" s="11"/>
+      <c r="AO21" s="11"/>
+      <c r="AP21" s="11"/>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.45">
       <c r="D22" s="9" t="s">
         <v>3</v>
       </c>
@@ -1722,42 +1710,16 @@
       <c r="AF22" s="8"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
-      <c r="AI22" s="66"/>
-      <c r="AJ22" s="66"/>
-      <c r="AK22" s="66"/>
-      <c r="AL22" s="66"/>
-      <c r="AM22" s="66"/>
-      <c r="AN22" s="66"/>
-      <c r="AO22" s="66"/>
-      <c r="AP22" s="66"/>
-      <c r="AQ22" s="67"/>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="U23" s="63"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="63"/>
-      <c r="X23" s="63"/>
-      <c r="Y23" s="63"/>
-      <c r="Z23" s="63"/>
-      <c r="AA23" s="63"/>
-      <c r="AB23" s="63"/>
-      <c r="AC23" s="63"/>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="63"/>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="63"/>
-      <c r="AH23" s="63"/>
-      <c r="AI23" s="63"/>
-      <c r="AJ23" s="63"/>
-      <c r="AK23" s="63"/>
-      <c r="AL23" s="63"/>
-      <c r="AM23" s="63"/>
-      <c r="AN23" s="63"/>
-      <c r="AO23" s="63"/>
-      <c r="AP23" s="63"/>
-      <c r="AQ23" s="67"/>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="8"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
+      <c r="AP22" s="8"/>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>4</v>
       </c>
@@ -1778,31 +1740,27 @@
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="T24" s="13"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64"/>
-      <c r="Z24" s="64"/>
-      <c r="AA24" s="64"/>
-      <c r="AB24" s="64"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="64"/>
-      <c r="AE24" s="64"/>
-      <c r="AF24" s="63"/>
-      <c r="AG24" s="65"/>
-      <c r="AH24" s="65"/>
-      <c r="AI24" s="65"/>
-      <c r="AJ24" s="64"/>
-      <c r="AK24" s="64"/>
-      <c r="AL24" s="64"/>
-      <c r="AM24" s="64"/>
-      <c r="AN24" s="64"/>
-      <c r="AO24" s="64"/>
-      <c r="AP24" s="64"/>
-      <c r="AQ24" s="67"/>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11"/>
+      <c r="AD24" s="11"/>
+      <c r="AE24" s="11"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="11"/>
+      <c r="AK24" s="11"/>
+      <c r="AL24" s="11"/>
+      <c r="AM24" s="11"/>
+      <c r="AN24" s="11"/>
+      <c r="AO24" s="11"/>
+      <c r="AP24" s="11"/>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.45">
       <c r="C25" s="9" t="s">
         <v>3</v>
       </c>
@@ -1825,31 +1783,30 @@
       <c r="R25" s="9"/>
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="66"/>
-      <c r="Z25" s="66"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="66"/>
-      <c r="AD25" s="66"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="66"/>
-      <c r="AJ25" s="66"/>
-      <c r="AK25" s="66"/>
-      <c r="AL25" s="66"/>
-      <c r="AM25" s="66"/>
-      <c r="AN25" s="66"/>
-      <c r="AO25" s="66"/>
-      <c r="AP25" s="66"/>
-      <c r="AQ25" s="67"/>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+      <c r="AP25" s="8"/>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.45">
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -1868,31 +1825,30 @@
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
       <c r="T26" s="8"/>
-      <c r="U26" s="66"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
-      <c r="Z26" s="66"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="66"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="66"/>
-      <c r="AJ26" s="66"/>
-      <c r="AK26" s="66"/>
-      <c r="AL26" s="66"/>
-      <c r="AM26" s="66"/>
-      <c r="AN26" s="66"/>
-      <c r="AO26" s="66"/>
-      <c r="AP26" s="66"/>
-      <c r="AQ26" s="67"/>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8"/>
+      <c r="AD26" s="8"/>
+      <c r="AE26" s="8"/>
+      <c r="AF26" s="8"/>
+      <c r="AG26" s="8"/>
+      <c r="AH26" s="8"/>
+      <c r="AI26" s="8"/>
+      <c r="AJ26" s="8"/>
+      <c r="AK26" s="8"/>
+      <c r="AL26" s="8"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
+      <c r="AP26" s="8"/>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.45">
       <c r="F27" s="7" t="s">
         <v>1</v>
       </c>
@@ -1914,23 +1870,28 @@
       <c r="R27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="AI27" s="63"/>
-      <c r="AJ27" s="63"/>
-      <c r="AK27" s="63"/>
-      <c r="AL27" s="63"/>
-      <c r="AM27" s="63"/>
-      <c r="AN27" s="63"/>
-      <c r="AO27" s="63"/>
-      <c r="AP27" s="63"/>
-      <c r="AQ27" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="AA14:AD14"/>
-    <mergeCell ref="AE14:AG14"/>
-    <mergeCell ref="AH14:AI14"/>
-    <mergeCell ref="AJ14:AM14"/>
-    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="AN15:AP15"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="G15:L15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="AA15:AD15"/>
+    <mergeCell ref="AE15:AG15"/>
+    <mergeCell ref="AH15:AI15"/>
+    <mergeCell ref="AJ15:AM15"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AN5:AP5"/>
+    <mergeCell ref="U6:AE6"/>
+    <mergeCell ref="AJ6:AL6"/>
+    <mergeCell ref="AN6:AP6"/>
     <mergeCell ref="X14:Z14"/>
     <mergeCell ref="E12:AL12"/>
     <mergeCell ref="AN12:AP12"/>
@@ -1944,28 +1905,14 @@
     <mergeCell ref="AN10:AP10"/>
     <mergeCell ref="F11:AL11"/>
     <mergeCell ref="AN11:AP11"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AN5:AP5"/>
-    <mergeCell ref="U6:AE6"/>
-    <mergeCell ref="AJ6:AL6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="AA15:AD15"/>
-    <mergeCell ref="AE15:AG15"/>
-    <mergeCell ref="AH15:AI15"/>
-    <mergeCell ref="AJ15:AM15"/>
-    <mergeCell ref="AN15:AP15"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="U15:W15"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="G14:L14"/>
     <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="AA14:AD14"/>
+    <mergeCell ref="AE14:AG14"/>
+    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="AJ14:AM14"/>
+    <mergeCell ref="AN14:AP14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
